--- a/Pemindah JD adaptif V6/TemplateJobDescBaruKosongan/Template GOL 4_Managerial.xlsx
+++ b/Pemindah JD adaptif V6/TemplateJobDescBaruKosongan/Template GOL 4_Managerial.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\titipan Feli\PROYEK GEDE\Database\Template Baru kosong\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\z\TemplateJobDescBaruKosongan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023595C2-DDC2-4ADB-BCA3-9DEB99A33B73}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF8959C-53D3-49E0-AF3A-90F48C33162C}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{B4CA32BC-DA9F-4539-8D41-F96D4CBDAEFA}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="65">
   <si>
     <t>JOB DESCRIPTION</t>
   </si>
@@ -201,9 +201,6 @@
     </r>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>DivisionName</t>
   </si>
   <si>
@@ -243,16 +240,10 @@
     <t>TugasPokokSpecificMoved</t>
   </si>
   <si>
-    <t>1.</t>
-  </si>
-  <si>
-    <t>2.</t>
-  </si>
-  <si>
-    <t>3.</t>
-  </si>
-  <si>
     <t>ExternalXYZConnection</t>
+  </si>
+  <si>
+    <t>ExternalConnection</t>
   </si>
 </sst>
 </file>
@@ -626,7 +617,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1042,6 +1033,42 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1069,15 +1096,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1105,32 +1123,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1611,37 +1605,37 @@
       <c r="J2" s="45"/>
       <c r="K2" s="45"/>
       <c r="L2" s="46"/>
-      <c r="M2" s="147" t="s">
+      <c r="M2" s="159" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="148"/>
-      <c r="O2" s="148"/>
-      <c r="P2" s="148"/>
-      <c r="Q2" s="148"/>
-      <c r="R2" s="148"/>
-      <c r="S2" s="148"/>
-      <c r="T2" s="148"/>
-      <c r="U2" s="148"/>
-      <c r="V2" s="148"/>
-      <c r="W2" s="148"/>
-      <c r="X2" s="148"/>
-      <c r="Y2" s="148"/>
-      <c r="Z2" s="148"/>
-      <c r="AA2" s="148"/>
-      <c r="AB2" s="148"/>
-      <c r="AC2" s="148"/>
-      <c r="AD2" s="148"/>
-      <c r="AE2" s="148"/>
-      <c r="AF2" s="148"/>
-      <c r="AG2" s="148"/>
-      <c r="AH2" s="148"/>
-      <c r="AI2" s="148"/>
-      <c r="AJ2" s="148"/>
-      <c r="AK2" s="148"/>
-      <c r="AL2" s="148"/>
-      <c r="AM2" s="148"/>
-      <c r="AN2" s="148"/>
-      <c r="AO2" s="149"/>
+      <c r="N2" s="160"/>
+      <c r="O2" s="160"/>
+      <c r="P2" s="160"/>
+      <c r="Q2" s="160"/>
+      <c r="R2" s="160"/>
+      <c r="S2" s="160"/>
+      <c r="T2" s="160"/>
+      <c r="U2" s="160"/>
+      <c r="V2" s="160"/>
+      <c r="W2" s="160"/>
+      <c r="X2" s="160"/>
+      <c r="Y2" s="160"/>
+      <c r="Z2" s="160"/>
+      <c r="AA2" s="160"/>
+      <c r="AB2" s="160"/>
+      <c r="AC2" s="160"/>
+      <c r="AD2" s="160"/>
+      <c r="AE2" s="160"/>
+      <c r="AF2" s="160"/>
+      <c r="AG2" s="160"/>
+      <c r="AH2" s="160"/>
+      <c r="AI2" s="160"/>
+      <c r="AJ2" s="160"/>
+      <c r="AK2" s="160"/>
+      <c r="AL2" s="160"/>
+      <c r="AM2" s="160"/>
+      <c r="AN2" s="160"/>
+      <c r="AO2" s="161"/>
       <c r="AP2" s="126"/>
       <c r="AQ2" s="47" t="s">
         <v>1</v>
@@ -1654,7 +1648,7 @@
         <v>2</v>
       </c>
       <c r="AW2" s="127" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AX2" s="47"/>
       <c r="AY2" s="47"/>
@@ -1675,35 +1669,35 @@
     <row r="3" spans="2:68" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="30"/>
       <c r="L3" s="19"/>
-      <c r="M3" s="150"/>
-      <c r="N3" s="151"/>
-      <c r="O3" s="151"/>
-      <c r="P3" s="151"/>
-      <c r="Q3" s="151"/>
-      <c r="R3" s="151"/>
-      <c r="S3" s="151"/>
-      <c r="T3" s="151"/>
-      <c r="U3" s="151"/>
-      <c r="V3" s="151"/>
-      <c r="W3" s="151"/>
-      <c r="X3" s="151"/>
-      <c r="Y3" s="151"/>
-      <c r="Z3" s="151"/>
-      <c r="AA3" s="151"/>
-      <c r="AB3" s="151"/>
-      <c r="AC3" s="151"/>
-      <c r="AD3" s="151"/>
-      <c r="AE3" s="151"/>
-      <c r="AF3" s="151"/>
-      <c r="AG3" s="151"/>
-      <c r="AH3" s="151"/>
-      <c r="AI3" s="151"/>
-      <c r="AJ3" s="151"/>
-      <c r="AK3" s="151"/>
-      <c r="AL3" s="151"/>
-      <c r="AM3" s="151"/>
-      <c r="AN3" s="151"/>
-      <c r="AO3" s="152"/>
+      <c r="M3" s="162"/>
+      <c r="N3" s="163"/>
+      <c r="O3" s="163"/>
+      <c r="P3" s="163"/>
+      <c r="Q3" s="163"/>
+      <c r="R3" s="163"/>
+      <c r="S3" s="163"/>
+      <c r="T3" s="163"/>
+      <c r="U3" s="163"/>
+      <c r="V3" s="163"/>
+      <c r="W3" s="163"/>
+      <c r="X3" s="163"/>
+      <c r="Y3" s="163"/>
+      <c r="Z3" s="163"/>
+      <c r="AA3" s="163"/>
+      <c r="AB3" s="163"/>
+      <c r="AC3" s="163"/>
+      <c r="AD3" s="163"/>
+      <c r="AE3" s="163"/>
+      <c r="AF3" s="163"/>
+      <c r="AG3" s="163"/>
+      <c r="AH3" s="163"/>
+      <c r="AI3" s="163"/>
+      <c r="AJ3" s="163"/>
+      <c r="AK3" s="163"/>
+      <c r="AL3" s="163"/>
+      <c r="AM3" s="163"/>
+      <c r="AN3" s="163"/>
+      <c r="AO3" s="164"/>
       <c r="AP3" s="128"/>
       <c r="AQ3" s="50"/>
       <c r="AR3" s="50"/>
@@ -1730,35 +1724,35 @@
     <row r="4" spans="2:68" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="30"/>
       <c r="L4" s="19"/>
-      <c r="M4" s="150"/>
-      <c r="N4" s="151"/>
-      <c r="O4" s="151"/>
-      <c r="P4" s="151"/>
-      <c r="Q4" s="151"/>
-      <c r="R4" s="151"/>
-      <c r="S4" s="151"/>
-      <c r="T4" s="151"/>
-      <c r="U4" s="151"/>
-      <c r="V4" s="151"/>
-      <c r="W4" s="151"/>
-      <c r="X4" s="151"/>
-      <c r="Y4" s="151"/>
-      <c r="Z4" s="151"/>
-      <c r="AA4" s="151"/>
-      <c r="AB4" s="151"/>
-      <c r="AC4" s="151"/>
-      <c r="AD4" s="151"/>
-      <c r="AE4" s="151"/>
-      <c r="AF4" s="151"/>
-      <c r="AG4" s="151"/>
-      <c r="AH4" s="151"/>
-      <c r="AI4" s="151"/>
-      <c r="AJ4" s="151"/>
-      <c r="AK4" s="151"/>
-      <c r="AL4" s="151"/>
-      <c r="AM4" s="151"/>
-      <c r="AN4" s="151"/>
-      <c r="AO4" s="152"/>
+      <c r="M4" s="162"/>
+      <c r="N4" s="163"/>
+      <c r="O4" s="163"/>
+      <c r="P4" s="163"/>
+      <c r="Q4" s="163"/>
+      <c r="R4" s="163"/>
+      <c r="S4" s="163"/>
+      <c r="T4" s="163"/>
+      <c r="U4" s="163"/>
+      <c r="V4" s="163"/>
+      <c r="W4" s="163"/>
+      <c r="X4" s="163"/>
+      <c r="Y4" s="163"/>
+      <c r="Z4" s="163"/>
+      <c r="AA4" s="163"/>
+      <c r="AB4" s="163"/>
+      <c r="AC4" s="163"/>
+      <c r="AD4" s="163"/>
+      <c r="AE4" s="163"/>
+      <c r="AF4" s="163"/>
+      <c r="AG4" s="163"/>
+      <c r="AH4" s="163"/>
+      <c r="AI4" s="163"/>
+      <c r="AJ4" s="163"/>
+      <c r="AK4" s="163"/>
+      <c r="AL4" s="163"/>
+      <c r="AM4" s="163"/>
+      <c r="AN4" s="163"/>
+      <c r="AO4" s="164"/>
       <c r="AP4" s="128"/>
       <c r="AQ4" s="50" t="s">
         <v>3</v>
@@ -1771,7 +1765,7 @@
         <v>2</v>
       </c>
       <c r="AW4" s="129" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AX4" s="50"/>
       <c r="AY4" s="50"/>
@@ -1801,35 +1795,35 @@
       <c r="J5" s="29"/>
       <c r="K5" s="29"/>
       <c r="L5" s="53"/>
-      <c r="M5" s="153"/>
-      <c r="N5" s="154"/>
-      <c r="O5" s="154"/>
-      <c r="P5" s="154"/>
-      <c r="Q5" s="154"/>
-      <c r="R5" s="154"/>
-      <c r="S5" s="154"/>
-      <c r="T5" s="154"/>
-      <c r="U5" s="154"/>
-      <c r="V5" s="154"/>
-      <c r="W5" s="154"/>
-      <c r="X5" s="154"/>
-      <c r="Y5" s="154"/>
-      <c r="Z5" s="154"/>
-      <c r="AA5" s="154"/>
-      <c r="AB5" s="154"/>
-      <c r="AC5" s="154"/>
-      <c r="AD5" s="154"/>
-      <c r="AE5" s="154"/>
-      <c r="AF5" s="154"/>
-      <c r="AG5" s="154"/>
-      <c r="AH5" s="154"/>
-      <c r="AI5" s="154"/>
-      <c r="AJ5" s="154"/>
-      <c r="AK5" s="154"/>
-      <c r="AL5" s="154"/>
-      <c r="AM5" s="154"/>
-      <c r="AN5" s="154"/>
-      <c r="AO5" s="155"/>
+      <c r="M5" s="165"/>
+      <c r="N5" s="166"/>
+      <c r="O5" s="166"/>
+      <c r="P5" s="166"/>
+      <c r="Q5" s="166"/>
+      <c r="R5" s="166"/>
+      <c r="S5" s="166"/>
+      <c r="T5" s="166"/>
+      <c r="U5" s="166"/>
+      <c r="V5" s="166"/>
+      <c r="W5" s="166"/>
+      <c r="X5" s="166"/>
+      <c r="Y5" s="166"/>
+      <c r="Z5" s="166"/>
+      <c r="AA5" s="166"/>
+      <c r="AB5" s="166"/>
+      <c r="AC5" s="166"/>
+      <c r="AD5" s="166"/>
+      <c r="AE5" s="166"/>
+      <c r="AF5" s="166"/>
+      <c r="AG5" s="166"/>
+      <c r="AH5" s="166"/>
+      <c r="AI5" s="166"/>
+      <c r="AJ5" s="166"/>
+      <c r="AK5" s="166"/>
+      <c r="AL5" s="166"/>
+      <c r="AM5" s="166"/>
+      <c r="AN5" s="166"/>
+      <c r="AO5" s="167"/>
       <c r="AP5" s="130"/>
       <c r="AQ5" s="54" t="s">
         <v>4</v>
@@ -1842,7 +1836,7 @@
         <v>2</v>
       </c>
       <c r="AW5" s="29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AX5" s="54"/>
       <c r="AY5" s="54"/>
@@ -1992,99 +1986,99 @@
       <c r="BP7" s="10"/>
     </row>
     <row r="8" spans="2:68" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="156" t="s">
+      <c r="B8" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="157"/>
-      <c r="D8" s="157"/>
-      <c r="E8" s="157"/>
-      <c r="F8" s="157"/>
-      <c r="G8" s="157"/>
-      <c r="H8" s="157"/>
-      <c r="I8" s="157"/>
-      <c r="J8" s="157"/>
-      <c r="K8" s="157"/>
-      <c r="L8" s="157"/>
-      <c r="M8" s="157"/>
-      <c r="N8" s="157"/>
-      <c r="O8" s="157"/>
-      <c r="P8" s="157"/>
-      <c r="Q8" s="157"/>
-      <c r="R8" s="157"/>
-      <c r="S8" s="157"/>
-      <c r="T8" s="157"/>
-      <c r="U8" s="157"/>
-      <c r="V8" s="157"/>
-      <c r="W8" s="158"/>
-      <c r="X8" s="156" t="s">
+      <c r="C8" s="151"/>
+      <c r="D8" s="151"/>
+      <c r="E8" s="151"/>
+      <c r="F8" s="151"/>
+      <c r="G8" s="151"/>
+      <c r="H8" s="151"/>
+      <c r="I8" s="151"/>
+      <c r="J8" s="151"/>
+      <c r="K8" s="151"/>
+      <c r="L8" s="151"/>
+      <c r="M8" s="151"/>
+      <c r="N8" s="151"/>
+      <c r="O8" s="151"/>
+      <c r="P8" s="151"/>
+      <c r="Q8" s="151"/>
+      <c r="R8" s="151"/>
+      <c r="S8" s="151"/>
+      <c r="T8" s="151"/>
+      <c r="U8" s="151"/>
+      <c r="V8" s="151"/>
+      <c r="W8" s="152"/>
+      <c r="X8" s="150" t="s">
         <v>6</v>
       </c>
-      <c r="Y8" s="157"/>
-      <c r="Z8" s="157"/>
-      <c r="AA8" s="157"/>
-      <c r="AB8" s="157"/>
-      <c r="AC8" s="157"/>
-      <c r="AD8" s="157"/>
-      <c r="AE8" s="157"/>
-      <c r="AF8" s="157"/>
-      <c r="AG8" s="157"/>
-      <c r="AH8" s="157"/>
-      <c r="AI8" s="157"/>
-      <c r="AJ8" s="157"/>
-      <c r="AK8" s="157"/>
-      <c r="AL8" s="157"/>
-      <c r="AM8" s="157"/>
-      <c r="AN8" s="157"/>
-      <c r="AO8" s="158"/>
+      <c r="Y8" s="151"/>
+      <c r="Z8" s="151"/>
+      <c r="AA8" s="151"/>
+      <c r="AB8" s="151"/>
+      <c r="AC8" s="151"/>
+      <c r="AD8" s="151"/>
+      <c r="AE8" s="151"/>
+      <c r="AF8" s="151"/>
+      <c r="AG8" s="151"/>
+      <c r="AH8" s="151"/>
+      <c r="AI8" s="151"/>
+      <c r="AJ8" s="151"/>
+      <c r="AK8" s="151"/>
+      <c r="AL8" s="151"/>
+      <c r="AM8" s="151"/>
+      <c r="AN8" s="151"/>
+      <c r="AO8" s="152"/>
       <c r="AP8" s="65"/>
-      <c r="AQ8" s="156" t="s">
+      <c r="AQ8" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="AR8" s="157"/>
-      <c r="AS8" s="157"/>
-      <c r="AT8" s="157"/>
-      <c r="AU8" s="157"/>
-      <c r="AV8" s="157"/>
-      <c r="AW8" s="157"/>
-      <c r="AX8" s="157"/>
-      <c r="AY8" s="157"/>
-      <c r="AZ8" s="157"/>
-      <c r="BA8" s="157"/>
-      <c r="BB8" s="157"/>
-      <c r="BC8" s="157"/>
-      <c r="BD8" s="157"/>
-      <c r="BE8" s="157"/>
-      <c r="BF8" s="157"/>
-      <c r="BG8" s="157"/>
-      <c r="BH8" s="157"/>
-      <c r="BI8" s="157"/>
-      <c r="BJ8" s="157"/>
-      <c r="BK8" s="158"/>
+      <c r="AR8" s="151"/>
+      <c r="AS8" s="151"/>
+      <c r="AT8" s="151"/>
+      <c r="AU8" s="151"/>
+      <c r="AV8" s="151"/>
+      <c r="AW8" s="151"/>
+      <c r="AX8" s="151"/>
+      <c r="AY8" s="151"/>
+      <c r="AZ8" s="151"/>
+      <c r="BA8" s="151"/>
+      <c r="BB8" s="151"/>
+      <c r="BC8" s="151"/>
+      <c r="BD8" s="151"/>
+      <c r="BE8" s="151"/>
+      <c r="BF8" s="151"/>
+      <c r="BG8" s="151"/>
+      <c r="BH8" s="151"/>
+      <c r="BI8" s="151"/>
+      <c r="BJ8" s="151"/>
+      <c r="BK8" s="152"/>
       <c r="BL8" s="32"/>
       <c r="BN8" s="10"/>
     </row>
     <row r="9" spans="2:68" ht="16.7" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="30"/>
-      <c r="X9" s="159" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y9" s="160"/>
-      <c r="Z9" s="160"/>
-      <c r="AA9" s="160"/>
-      <c r="AB9" s="160"/>
-      <c r="AC9" s="160"/>
-      <c r="AD9" s="160"/>
-      <c r="AE9" s="160"/>
-      <c r="AF9" s="160"/>
-      <c r="AG9" s="160"/>
-      <c r="AH9" s="160"/>
-      <c r="AI9" s="160"/>
-      <c r="AJ9" s="160"/>
-      <c r="AK9" s="160"/>
-      <c r="AL9" s="160"/>
-      <c r="AM9" s="160"/>
-      <c r="AN9" s="160"/>
-      <c r="AO9" s="161"/>
+      <c r="X9" s="168" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y9" s="169"/>
+      <c r="Z9" s="169"/>
+      <c r="AA9" s="169"/>
+      <c r="AB9" s="169"/>
+      <c r="AC9" s="169"/>
+      <c r="AD9" s="169"/>
+      <c r="AE9" s="169"/>
+      <c r="AF9" s="169"/>
+      <c r="AG9" s="169"/>
+      <c r="AH9" s="169"/>
+      <c r="AI9" s="169"/>
+      <c r="AJ9" s="169"/>
+      <c r="AK9" s="169"/>
+      <c r="AL9" s="169"/>
+      <c r="AM9" s="169"/>
+      <c r="AN9" s="169"/>
+      <c r="AO9" s="170"/>
       <c r="AP9" s="30"/>
       <c r="AQ9" s="66" t="s">
         <v>8</v>
@@ -2095,24 +2089,24 @@
     </row>
     <row r="10" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="30"/>
-      <c r="X10" s="162"/>
-      <c r="Y10" s="163"/>
-      <c r="Z10" s="163"/>
-      <c r="AA10" s="163"/>
-      <c r="AB10" s="163"/>
-      <c r="AC10" s="163"/>
-      <c r="AD10" s="163"/>
-      <c r="AE10" s="163"/>
-      <c r="AF10" s="163"/>
-      <c r="AG10" s="163"/>
-      <c r="AH10" s="163"/>
-      <c r="AI10" s="163"/>
-      <c r="AJ10" s="163"/>
-      <c r="AK10" s="163"/>
-      <c r="AL10" s="163"/>
-      <c r="AM10" s="163"/>
-      <c r="AN10" s="163"/>
-      <c r="AO10" s="164"/>
+      <c r="X10" s="171"/>
+      <c r="Y10" s="172"/>
+      <c r="Z10" s="172"/>
+      <c r="AA10" s="172"/>
+      <c r="AB10" s="172"/>
+      <c r="AC10" s="172"/>
+      <c r="AD10" s="172"/>
+      <c r="AE10" s="172"/>
+      <c r="AF10" s="172"/>
+      <c r="AG10" s="172"/>
+      <c r="AH10" s="172"/>
+      <c r="AI10" s="172"/>
+      <c r="AJ10" s="172"/>
+      <c r="AK10" s="172"/>
+      <c r="AL10" s="172"/>
+      <c r="AM10" s="172"/>
+      <c r="AN10" s="172"/>
+      <c r="AO10" s="173"/>
       <c r="AP10" s="67"/>
       <c r="AQ10" s="7"/>
       <c r="AR10" s="10"/>
@@ -2122,24 +2116,24 @@
     <row r="11" spans="2:68" ht="16.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="30"/>
       <c r="W11" s="19"/>
-      <c r="X11" s="165"/>
-      <c r="Y11" s="166"/>
-      <c r="Z11" s="166"/>
-      <c r="AA11" s="166"/>
-      <c r="AB11" s="166"/>
-      <c r="AC11" s="166"/>
-      <c r="AD11" s="166"/>
-      <c r="AE11" s="166"/>
-      <c r="AF11" s="166"/>
-      <c r="AG11" s="166"/>
-      <c r="AH11" s="166"/>
-      <c r="AI11" s="166"/>
-      <c r="AJ11" s="166"/>
-      <c r="AK11" s="166"/>
-      <c r="AL11" s="166"/>
-      <c r="AM11" s="166"/>
-      <c r="AN11" s="166"/>
-      <c r="AO11" s="167"/>
+      <c r="X11" s="174"/>
+      <c r="Y11" s="175"/>
+      <c r="Z11" s="175"/>
+      <c r="AA11" s="175"/>
+      <c r="AB11" s="175"/>
+      <c r="AC11" s="175"/>
+      <c r="AD11" s="175"/>
+      <c r="AE11" s="175"/>
+      <c r="AF11" s="175"/>
+      <c r="AG11" s="175"/>
+      <c r="AH11" s="175"/>
+      <c r="AI11" s="175"/>
+      <c r="AJ11" s="175"/>
+      <c r="AK11" s="175"/>
+      <c r="AL11" s="175"/>
+      <c r="AM11" s="175"/>
+      <c r="AN11" s="175"/>
+      <c r="AO11" s="176"/>
       <c r="AP11" s="67"/>
       <c r="AQ11" s="14"/>
       <c r="BK11" s="19"/>
@@ -2148,26 +2142,26 @@
     <row r="12" spans="2:68" ht="16.7" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="30"/>
       <c r="W12" s="19"/>
-      <c r="X12" s="156" t="s">
+      <c r="X12" s="150" t="s">
         <v>9</v>
       </c>
-      <c r="Y12" s="157"/>
-      <c r="Z12" s="157"/>
-      <c r="AA12" s="157"/>
-      <c r="AB12" s="157"/>
-      <c r="AC12" s="157"/>
-      <c r="AD12" s="157"/>
-      <c r="AE12" s="157"/>
-      <c r="AF12" s="157"/>
-      <c r="AG12" s="157"/>
-      <c r="AH12" s="157"/>
-      <c r="AI12" s="157"/>
-      <c r="AJ12" s="157"/>
-      <c r="AK12" s="157"/>
-      <c r="AL12" s="157"/>
-      <c r="AM12" s="157"/>
-      <c r="AN12" s="157"/>
-      <c r="AO12" s="158"/>
+      <c r="Y12" s="151"/>
+      <c r="Z12" s="151"/>
+      <c r="AA12" s="151"/>
+      <c r="AB12" s="151"/>
+      <c r="AC12" s="151"/>
+      <c r="AD12" s="151"/>
+      <c r="AE12" s="151"/>
+      <c r="AF12" s="151"/>
+      <c r="AG12" s="151"/>
+      <c r="AH12" s="151"/>
+      <c r="AI12" s="151"/>
+      <c r="AJ12" s="151"/>
+      <c r="AK12" s="151"/>
+      <c r="AL12" s="151"/>
+      <c r="AM12" s="151"/>
+      <c r="AN12" s="151"/>
+      <c r="AO12" s="152"/>
       <c r="AP12" s="67"/>
       <c r="AQ12" s="32" t="s">
         <v>10</v>
@@ -2426,14 +2420,14 @@
       <c r="K22" s="29"/>
       <c r="L22" s="29"/>
       <c r="M22" s="29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N22" s="29"/>
       <c r="O22" s="29"/>
       <c r="P22" s="29"/>
       <c r="Q22" s="29"/>
       <c r="R22" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S22" s="29"/>
       <c r="T22" s="29"/>
@@ -2483,70 +2477,70 @@
       <c r="BN22" s="10"/>
     </row>
     <row r="23" spans="2:68" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="156" t="s">
+      <c r="B23" s="150" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="157"/>
-      <c r="D23" s="157"/>
-      <c r="E23" s="157"/>
-      <c r="F23" s="157"/>
-      <c r="G23" s="157"/>
-      <c r="H23" s="157"/>
-      <c r="I23" s="157"/>
-      <c r="J23" s="157"/>
-      <c r="K23" s="157"/>
-      <c r="L23" s="157"/>
-      <c r="M23" s="157"/>
-      <c r="N23" s="157"/>
-      <c r="O23" s="157"/>
-      <c r="P23" s="157"/>
-      <c r="Q23" s="157"/>
-      <c r="R23" s="157"/>
-      <c r="S23" s="157"/>
-      <c r="T23" s="157"/>
-      <c r="U23" s="157"/>
-      <c r="V23" s="157"/>
-      <c r="W23" s="157"/>
-      <c r="X23" s="157"/>
-      <c r="Y23" s="157"/>
-      <c r="Z23" s="157"/>
-      <c r="AA23" s="157"/>
-      <c r="AB23" s="157"/>
-      <c r="AC23" s="157"/>
-      <c r="AD23" s="157"/>
-      <c r="AE23" s="157"/>
-      <c r="AF23" s="157"/>
-      <c r="AG23" s="157"/>
-      <c r="AH23" s="157"/>
-      <c r="AI23" s="157"/>
-      <c r="AJ23" s="157"/>
-      <c r="AK23" s="157"/>
-      <c r="AL23" s="157"/>
-      <c r="AM23" s="157"/>
-      <c r="AN23" s="157"/>
-      <c r="AO23" s="157"/>
-      <c r="AP23" s="157"/>
-      <c r="AQ23" s="157"/>
-      <c r="AR23" s="157"/>
-      <c r="AS23" s="157"/>
-      <c r="AT23" s="157"/>
-      <c r="AU23" s="157"/>
-      <c r="AV23" s="157"/>
-      <c r="AW23" s="157"/>
-      <c r="AX23" s="157"/>
-      <c r="AY23" s="157"/>
-      <c r="AZ23" s="157"/>
-      <c r="BA23" s="157"/>
-      <c r="BB23" s="157"/>
-      <c r="BC23" s="157"/>
-      <c r="BD23" s="157"/>
-      <c r="BE23" s="157"/>
-      <c r="BF23" s="157"/>
-      <c r="BG23" s="157"/>
-      <c r="BH23" s="157"/>
-      <c r="BI23" s="157"/>
-      <c r="BJ23" s="157"/>
-      <c r="BK23" s="158"/>
+      <c r="C23" s="151"/>
+      <c r="D23" s="151"/>
+      <c r="E23" s="151"/>
+      <c r="F23" s="151"/>
+      <c r="G23" s="151"/>
+      <c r="H23" s="151"/>
+      <c r="I23" s="151"/>
+      <c r="J23" s="151"/>
+      <c r="K23" s="151"/>
+      <c r="L23" s="151"/>
+      <c r="M23" s="151"/>
+      <c r="N23" s="151"/>
+      <c r="O23" s="151"/>
+      <c r="P23" s="151"/>
+      <c r="Q23" s="151"/>
+      <c r="R23" s="151"/>
+      <c r="S23" s="151"/>
+      <c r="T23" s="151"/>
+      <c r="U23" s="151"/>
+      <c r="V23" s="151"/>
+      <c r="W23" s="151"/>
+      <c r="X23" s="151"/>
+      <c r="Y23" s="151"/>
+      <c r="Z23" s="151"/>
+      <c r="AA23" s="151"/>
+      <c r="AB23" s="151"/>
+      <c r="AC23" s="151"/>
+      <c r="AD23" s="151"/>
+      <c r="AE23" s="151"/>
+      <c r="AF23" s="151"/>
+      <c r="AG23" s="151"/>
+      <c r="AH23" s="151"/>
+      <c r="AI23" s="151"/>
+      <c r="AJ23" s="151"/>
+      <c r="AK23" s="151"/>
+      <c r="AL23" s="151"/>
+      <c r="AM23" s="151"/>
+      <c r="AN23" s="151"/>
+      <c r="AO23" s="151"/>
+      <c r="AP23" s="151"/>
+      <c r="AQ23" s="151"/>
+      <c r="AR23" s="151"/>
+      <c r="AS23" s="151"/>
+      <c r="AT23" s="151"/>
+      <c r="AU23" s="151"/>
+      <c r="AV23" s="151"/>
+      <c r="AW23" s="151"/>
+      <c r="AX23" s="151"/>
+      <c r="AY23" s="151"/>
+      <c r="AZ23" s="151"/>
+      <c r="BA23" s="151"/>
+      <c r="BB23" s="151"/>
+      <c r="BC23" s="151"/>
+      <c r="BD23" s="151"/>
+      <c r="BE23" s="151"/>
+      <c r="BF23" s="151"/>
+      <c r="BG23" s="151"/>
+      <c r="BH23" s="151"/>
+      <c r="BI23" s="151"/>
+      <c r="BJ23" s="151"/>
+      <c r="BK23" s="152"/>
     </row>
     <row r="24" spans="2:68" ht="16.7" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B24" s="73" t="s">
@@ -3064,7 +3058,7 @@
     </row>
     <row r="35" spans="1:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="144" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C35" s="138"/>
       <c r="D35" s="35"/>
@@ -3455,79 +3449,79 @@
       <c r="T43" s="32"/>
       <c r="AO43" s="19"/>
       <c r="AP43" s="70"/>
-      <c r="AQ43" s="176"/>
+      <c r="AQ43" s="148"/>
       <c r="AR43" s="7"/>
       <c r="BK43" s="19"/>
     </row>
     <row r="44" spans="1:68" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="175"/>
+      <c r="B44" s="147"/>
       <c r="C44" s="84"/>
       <c r="D44" s="12"/>
     </row>
     <row r="45" spans="1:68" s="32" customFormat="1" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>
-      <c r="B45" s="170"/>
-      <c r="C45" s="170"/>
-      <c r="D45" s="170"/>
-      <c r="E45" s="170"/>
-      <c r="F45" s="170"/>
-      <c r="G45" s="170"/>
-      <c r="H45" s="170"/>
-      <c r="I45" s="170"/>
-      <c r="J45" s="170"/>
-      <c r="K45" s="170"/>
-      <c r="L45" s="170"/>
-      <c r="M45" s="170"/>
-      <c r="N45" s="170"/>
-      <c r="O45" s="170"/>
-      <c r="P45" s="170"/>
-      <c r="Q45" s="170"/>
-      <c r="R45" s="170"/>
-      <c r="S45" s="170"/>
-      <c r="T45" s="170"/>
-      <c r="U45" s="170"/>
-      <c r="V45" s="170"/>
-      <c r="W45" s="170"/>
-      <c r="X45" s="170"/>
-      <c r="Y45" s="170"/>
-      <c r="Z45" s="170"/>
-      <c r="AA45" s="170"/>
-      <c r="AB45" s="170"/>
-      <c r="AC45" s="170"/>
-      <c r="AD45" s="170"/>
-      <c r="AE45" s="170"/>
-      <c r="AF45" s="170"/>
-      <c r="AG45" s="170"/>
-      <c r="AH45" s="170"/>
-      <c r="AI45" s="170"/>
-      <c r="AJ45" s="170"/>
-      <c r="AK45" s="170"/>
-      <c r="AL45" s="170"/>
-      <c r="AM45" s="170"/>
-      <c r="AN45" s="170"/>
-      <c r="AO45" s="170"/>
-      <c r="AP45" s="170"/>
-      <c r="AQ45" s="170"/>
-      <c r="AR45" s="170"/>
-      <c r="AS45" s="170"/>
-      <c r="AT45" s="170"/>
-      <c r="AU45" s="170"/>
-      <c r="AV45" s="170"/>
-      <c r="AW45" s="170"/>
-      <c r="AX45" s="170"/>
-      <c r="AY45" s="170"/>
-      <c r="AZ45" s="170"/>
-      <c r="BA45" s="170"/>
-      <c r="BB45" s="170"/>
-      <c r="BC45" s="170"/>
-      <c r="BD45" s="170"/>
-      <c r="BE45" s="170"/>
-      <c r="BF45" s="170"/>
-      <c r="BG45" s="170"/>
-      <c r="BH45" s="170"/>
-      <c r="BI45" s="170"/>
-      <c r="BJ45" s="170"/>
-      <c r="BK45" s="170"/>
+      <c r="B45" s="155"/>
+      <c r="C45" s="155"/>
+      <c r="D45" s="155"/>
+      <c r="E45" s="155"/>
+      <c r="F45" s="155"/>
+      <c r="G45" s="155"/>
+      <c r="H45" s="155"/>
+      <c r="I45" s="155"/>
+      <c r="J45" s="155"/>
+      <c r="K45" s="155"/>
+      <c r="L45" s="155"/>
+      <c r="M45" s="155"/>
+      <c r="N45" s="155"/>
+      <c r="O45" s="155"/>
+      <c r="P45" s="155"/>
+      <c r="Q45" s="155"/>
+      <c r="R45" s="155"/>
+      <c r="S45" s="155"/>
+      <c r="T45" s="155"/>
+      <c r="U45" s="155"/>
+      <c r="V45" s="155"/>
+      <c r="W45" s="155"/>
+      <c r="X45" s="155"/>
+      <c r="Y45" s="155"/>
+      <c r="Z45" s="155"/>
+      <c r="AA45" s="155"/>
+      <c r="AB45" s="155"/>
+      <c r="AC45" s="155"/>
+      <c r="AD45" s="155"/>
+      <c r="AE45" s="155"/>
+      <c r="AF45" s="155"/>
+      <c r="AG45" s="155"/>
+      <c r="AH45" s="155"/>
+      <c r="AI45" s="155"/>
+      <c r="AJ45" s="155"/>
+      <c r="AK45" s="155"/>
+      <c r="AL45" s="155"/>
+      <c r="AM45" s="155"/>
+      <c r="AN45" s="155"/>
+      <c r="AO45" s="155"/>
+      <c r="AP45" s="155"/>
+      <c r="AQ45" s="155"/>
+      <c r="AR45" s="155"/>
+      <c r="AS45" s="155"/>
+      <c r="AT45" s="155"/>
+      <c r="AU45" s="155"/>
+      <c r="AV45" s="155"/>
+      <c r="AW45" s="155"/>
+      <c r="AX45" s="155"/>
+      <c r="AY45" s="155"/>
+      <c r="AZ45" s="155"/>
+      <c r="BA45" s="155"/>
+      <c r="BB45" s="155"/>
+      <c r="BC45" s="155"/>
+      <c r="BD45" s="155"/>
+      <c r="BE45" s="155"/>
+      <c r="BF45" s="155"/>
+      <c r="BG45" s="155"/>
+      <c r="BH45" s="155"/>
+      <c r="BI45" s="155"/>
+      <c r="BJ45" s="155"/>
+      <c r="BK45" s="155"/>
       <c r="BL45" s="13"/>
     </row>
     <row r="46" spans="1:68" ht="21.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
@@ -3542,37 +3536,37 @@
       <c r="J46" s="45"/>
       <c r="K46" s="45"/>
       <c r="L46" s="46"/>
-      <c r="M46" s="147" t="s">
+      <c r="M46" s="159" t="s">
         <v>0</v>
       </c>
-      <c r="N46" s="148"/>
-      <c r="O46" s="148"/>
-      <c r="P46" s="148"/>
-      <c r="Q46" s="148"/>
-      <c r="R46" s="148"/>
-      <c r="S46" s="148"/>
-      <c r="T46" s="148"/>
-      <c r="U46" s="148"/>
-      <c r="V46" s="148"/>
-      <c r="W46" s="148"/>
-      <c r="X46" s="148"/>
-      <c r="Y46" s="148"/>
-      <c r="Z46" s="148"/>
-      <c r="AA46" s="148"/>
-      <c r="AB46" s="148"/>
-      <c r="AC46" s="148"/>
-      <c r="AD46" s="148"/>
-      <c r="AE46" s="148"/>
-      <c r="AF46" s="148"/>
-      <c r="AG46" s="148"/>
-      <c r="AH46" s="148"/>
-      <c r="AI46" s="148"/>
-      <c r="AJ46" s="148"/>
-      <c r="AK46" s="148"/>
-      <c r="AL46" s="148"/>
-      <c r="AM46" s="148"/>
-      <c r="AN46" s="148"/>
-      <c r="AO46" s="149"/>
+      <c r="N46" s="160"/>
+      <c r="O46" s="160"/>
+      <c r="P46" s="160"/>
+      <c r="Q46" s="160"/>
+      <c r="R46" s="160"/>
+      <c r="S46" s="160"/>
+      <c r="T46" s="160"/>
+      <c r="U46" s="160"/>
+      <c r="V46" s="160"/>
+      <c r="W46" s="160"/>
+      <c r="X46" s="160"/>
+      <c r="Y46" s="160"/>
+      <c r="Z46" s="160"/>
+      <c r="AA46" s="160"/>
+      <c r="AB46" s="160"/>
+      <c r="AC46" s="160"/>
+      <c r="AD46" s="160"/>
+      <c r="AE46" s="160"/>
+      <c r="AF46" s="160"/>
+      <c r="AG46" s="160"/>
+      <c r="AH46" s="160"/>
+      <c r="AI46" s="160"/>
+      <c r="AJ46" s="160"/>
+      <c r="AK46" s="160"/>
+      <c r="AL46" s="160"/>
+      <c r="AM46" s="160"/>
+      <c r="AN46" s="160"/>
+      <c r="AO46" s="161"/>
       <c r="AP46" s="131"/>
       <c r="AQ46" s="47" t="str">
         <f>$AQ$2</f>
@@ -3609,35 +3603,35 @@
     <row r="47" spans="1:68" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="30"/>
       <c r="L47" s="19"/>
-      <c r="M47" s="150"/>
-      <c r="N47" s="151"/>
-      <c r="O47" s="151"/>
-      <c r="P47" s="151"/>
-      <c r="Q47" s="151"/>
-      <c r="R47" s="151"/>
-      <c r="S47" s="151"/>
-      <c r="T47" s="151"/>
-      <c r="U47" s="151"/>
-      <c r="V47" s="151"/>
-      <c r="W47" s="151"/>
-      <c r="X47" s="151"/>
-      <c r="Y47" s="151"/>
-      <c r="Z47" s="151"/>
-      <c r="AA47" s="151"/>
-      <c r="AB47" s="151"/>
-      <c r="AC47" s="151"/>
-      <c r="AD47" s="151"/>
-      <c r="AE47" s="151"/>
-      <c r="AF47" s="151"/>
-      <c r="AG47" s="151"/>
-      <c r="AH47" s="151"/>
-      <c r="AI47" s="151"/>
-      <c r="AJ47" s="151"/>
-      <c r="AK47" s="151"/>
-      <c r="AL47" s="151"/>
-      <c r="AM47" s="151"/>
-      <c r="AN47" s="151"/>
-      <c r="AO47" s="152"/>
+      <c r="M47" s="162"/>
+      <c r="N47" s="163"/>
+      <c r="O47" s="163"/>
+      <c r="P47" s="163"/>
+      <c r="Q47" s="163"/>
+      <c r="R47" s="163"/>
+      <c r="S47" s="163"/>
+      <c r="T47" s="163"/>
+      <c r="U47" s="163"/>
+      <c r="V47" s="163"/>
+      <c r="W47" s="163"/>
+      <c r="X47" s="163"/>
+      <c r="Y47" s="163"/>
+      <c r="Z47" s="163"/>
+      <c r="AA47" s="163"/>
+      <c r="AB47" s="163"/>
+      <c r="AC47" s="163"/>
+      <c r="AD47" s="163"/>
+      <c r="AE47" s="163"/>
+      <c r="AF47" s="163"/>
+      <c r="AG47" s="163"/>
+      <c r="AH47" s="163"/>
+      <c r="AI47" s="163"/>
+      <c r="AJ47" s="163"/>
+      <c r="AK47" s="163"/>
+      <c r="AL47" s="163"/>
+      <c r="AM47" s="163"/>
+      <c r="AN47" s="163"/>
+      <c r="AO47" s="164"/>
       <c r="AP47" s="132"/>
       <c r="AQ47" s="32" t="str">
         <f>$AQ$4</f>
@@ -3673,35 +3667,35 @@
     <row r="48" spans="1:68" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="30"/>
       <c r="L48" s="19"/>
-      <c r="M48" s="150"/>
-      <c r="N48" s="151"/>
-      <c r="O48" s="151"/>
-      <c r="P48" s="151"/>
-      <c r="Q48" s="151"/>
-      <c r="R48" s="151"/>
-      <c r="S48" s="151"/>
-      <c r="T48" s="151"/>
-      <c r="U48" s="151"/>
-      <c r="V48" s="151"/>
-      <c r="W48" s="151"/>
-      <c r="X48" s="151"/>
-      <c r="Y48" s="151"/>
-      <c r="Z48" s="151"/>
-      <c r="AA48" s="151"/>
-      <c r="AB48" s="151"/>
-      <c r="AC48" s="151"/>
-      <c r="AD48" s="151"/>
-      <c r="AE48" s="151"/>
-      <c r="AF48" s="151"/>
-      <c r="AG48" s="151"/>
-      <c r="AH48" s="151"/>
-      <c r="AI48" s="151"/>
-      <c r="AJ48" s="151"/>
-      <c r="AK48" s="151"/>
-      <c r="AL48" s="151"/>
-      <c r="AM48" s="151"/>
-      <c r="AN48" s="151"/>
-      <c r="AO48" s="152"/>
+      <c r="M48" s="162"/>
+      <c r="N48" s="163"/>
+      <c r="O48" s="163"/>
+      <c r="P48" s="163"/>
+      <c r="Q48" s="163"/>
+      <c r="R48" s="163"/>
+      <c r="S48" s="163"/>
+      <c r="T48" s="163"/>
+      <c r="U48" s="163"/>
+      <c r="V48" s="163"/>
+      <c r="W48" s="163"/>
+      <c r="X48" s="163"/>
+      <c r="Y48" s="163"/>
+      <c r="Z48" s="163"/>
+      <c r="AA48" s="163"/>
+      <c r="AB48" s="163"/>
+      <c r="AC48" s="163"/>
+      <c r="AD48" s="163"/>
+      <c r="AE48" s="163"/>
+      <c r="AF48" s="163"/>
+      <c r="AG48" s="163"/>
+      <c r="AH48" s="163"/>
+      <c r="AI48" s="163"/>
+      <c r="AJ48" s="163"/>
+      <c r="AK48" s="163"/>
+      <c r="AL48" s="163"/>
+      <c r="AM48" s="163"/>
+      <c r="AN48" s="163"/>
+      <c r="AO48" s="164"/>
       <c r="AP48" s="133"/>
       <c r="AQ48" s="50"/>
       <c r="AR48" s="50"/>
@@ -3738,35 +3732,35 @@
       <c r="J49" s="29"/>
       <c r="K49" s="29"/>
       <c r="L49" s="53"/>
-      <c r="M49" s="153"/>
-      <c r="N49" s="154"/>
-      <c r="O49" s="154"/>
-      <c r="P49" s="154"/>
-      <c r="Q49" s="154"/>
-      <c r="R49" s="154"/>
-      <c r="S49" s="154"/>
-      <c r="T49" s="154"/>
-      <c r="U49" s="154"/>
-      <c r="V49" s="154"/>
-      <c r="W49" s="154"/>
-      <c r="X49" s="154"/>
-      <c r="Y49" s="154"/>
-      <c r="Z49" s="154"/>
-      <c r="AA49" s="154"/>
-      <c r="AB49" s="154"/>
-      <c r="AC49" s="154"/>
-      <c r="AD49" s="154"/>
-      <c r="AE49" s="154"/>
-      <c r="AF49" s="154"/>
-      <c r="AG49" s="154"/>
-      <c r="AH49" s="154"/>
-      <c r="AI49" s="154"/>
-      <c r="AJ49" s="154"/>
-      <c r="AK49" s="154"/>
-      <c r="AL49" s="154"/>
-      <c r="AM49" s="154"/>
-      <c r="AN49" s="154"/>
-      <c r="AO49" s="155"/>
+      <c r="M49" s="165"/>
+      <c r="N49" s="166"/>
+      <c r="O49" s="166"/>
+      <c r="P49" s="166"/>
+      <c r="Q49" s="166"/>
+      <c r="R49" s="166"/>
+      <c r="S49" s="166"/>
+      <c r="T49" s="166"/>
+      <c r="U49" s="166"/>
+      <c r="V49" s="166"/>
+      <c r="W49" s="166"/>
+      <c r="X49" s="166"/>
+      <c r="Y49" s="166"/>
+      <c r="Z49" s="166"/>
+      <c r="AA49" s="166"/>
+      <c r="AB49" s="166"/>
+      <c r="AC49" s="166"/>
+      <c r="AD49" s="166"/>
+      <c r="AE49" s="166"/>
+      <c r="AF49" s="166"/>
+      <c r="AG49" s="166"/>
+      <c r="AH49" s="166"/>
+      <c r="AI49" s="166"/>
+      <c r="AJ49" s="166"/>
+      <c r="AK49" s="166"/>
+      <c r="AL49" s="166"/>
+      <c r="AM49" s="166"/>
+      <c r="AN49" s="166"/>
+      <c r="AO49" s="167"/>
       <c r="AP49" s="134"/>
       <c r="AQ49" s="54" t="str">
         <f>$AQ$5</f>
@@ -3869,74 +3863,74 @@
       <c r="BP51" s="10"/>
     </row>
     <row r="52" spans="2:87" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="171" t="s">
+      <c r="B52" s="156" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="172"/>
-      <c r="D52" s="172"/>
-      <c r="E52" s="172"/>
-      <c r="F52" s="172"/>
-      <c r="G52" s="172"/>
-      <c r="H52" s="172"/>
-      <c r="I52" s="172"/>
-      <c r="J52" s="172"/>
-      <c r="K52" s="172"/>
-      <c r="L52" s="172"/>
-      <c r="M52" s="172"/>
-      <c r="N52" s="172"/>
-      <c r="O52" s="172"/>
-      <c r="P52" s="172"/>
-      <c r="Q52" s="172"/>
-      <c r="R52" s="172"/>
-      <c r="S52" s="172"/>
-      <c r="T52" s="173"/>
+      <c r="C52" s="157"/>
+      <c r="D52" s="157"/>
+      <c r="E52" s="157"/>
+      <c r="F52" s="157"/>
+      <c r="G52" s="157"/>
+      <c r="H52" s="157"/>
+      <c r="I52" s="157"/>
+      <c r="J52" s="157"/>
+      <c r="K52" s="157"/>
+      <c r="L52" s="157"/>
+      <c r="M52" s="157"/>
+      <c r="N52" s="157"/>
+      <c r="O52" s="157"/>
+      <c r="P52" s="157"/>
+      <c r="Q52" s="157"/>
+      <c r="R52" s="157"/>
+      <c r="S52" s="157"/>
+      <c r="T52" s="158"/>
       <c r="U52" s="32"/>
-      <c r="V52" s="171" t="s">
+      <c r="V52" s="156" t="s">
         <v>17</v>
       </c>
-      <c r="W52" s="172"/>
-      <c r="X52" s="172"/>
-      <c r="Y52" s="172"/>
-      <c r="Z52" s="172"/>
-      <c r="AA52" s="172"/>
-      <c r="AB52" s="172"/>
-      <c r="AC52" s="172"/>
-      <c r="AD52" s="172"/>
-      <c r="AE52" s="172"/>
-      <c r="AF52" s="172"/>
-      <c r="AG52" s="172"/>
-      <c r="AH52" s="172"/>
-      <c r="AI52" s="172"/>
-      <c r="AJ52" s="172"/>
-      <c r="AK52" s="172"/>
-      <c r="AL52" s="172"/>
-      <c r="AM52" s="172"/>
-      <c r="AN52" s="172"/>
-      <c r="AO52" s="173"/>
+      <c r="W52" s="157"/>
+      <c r="X52" s="157"/>
+      <c r="Y52" s="157"/>
+      <c r="Z52" s="157"/>
+      <c r="AA52" s="157"/>
+      <c r="AB52" s="157"/>
+      <c r="AC52" s="157"/>
+      <c r="AD52" s="157"/>
+      <c r="AE52" s="157"/>
+      <c r="AF52" s="157"/>
+      <c r="AG52" s="157"/>
+      <c r="AH52" s="157"/>
+      <c r="AI52" s="157"/>
+      <c r="AJ52" s="157"/>
+      <c r="AK52" s="157"/>
+      <c r="AL52" s="157"/>
+      <c r="AM52" s="157"/>
+      <c r="AN52" s="157"/>
+      <c r="AO52" s="158"/>
       <c r="AP52" s="32"/>
-      <c r="AQ52" s="171" t="s">
+      <c r="AQ52" s="156" t="s">
         <v>18</v>
       </c>
-      <c r="AR52" s="172"/>
-      <c r="AS52" s="172"/>
-      <c r="AT52" s="172"/>
-      <c r="AU52" s="172"/>
-      <c r="AV52" s="172"/>
-      <c r="AW52" s="172"/>
-      <c r="AX52" s="172"/>
-      <c r="AY52" s="172"/>
-      <c r="AZ52" s="172"/>
-      <c r="BA52" s="172"/>
-      <c r="BB52" s="172"/>
-      <c r="BC52" s="172"/>
-      <c r="BD52" s="172"/>
-      <c r="BE52" s="172"/>
-      <c r="BF52" s="172"/>
-      <c r="BG52" s="172"/>
-      <c r="BH52" s="172"/>
-      <c r="BI52" s="172"/>
-      <c r="BJ52" s="172"/>
-      <c r="BK52" s="173"/>
+      <c r="AR52" s="157"/>
+      <c r="AS52" s="157"/>
+      <c r="AT52" s="157"/>
+      <c r="AU52" s="157"/>
+      <c r="AV52" s="157"/>
+      <c r="AW52" s="157"/>
+      <c r="AX52" s="157"/>
+      <c r="AY52" s="157"/>
+      <c r="AZ52" s="157"/>
+      <c r="BA52" s="157"/>
+      <c r="BB52" s="157"/>
+      <c r="BC52" s="157"/>
+      <c r="BD52" s="157"/>
+      <c r="BE52" s="157"/>
+      <c r="BF52" s="157"/>
+      <c r="BG52" s="157"/>
+      <c r="BH52" s="157"/>
+      <c r="BI52" s="157"/>
+      <c r="BJ52" s="157"/>
+      <c r="BK52" s="158"/>
       <c r="BN52" s="10"/>
       <c r="BO52" s="4"/>
       <c r="BP52" s="10"/>
@@ -3983,31 +3977,31 @@
       <c r="BH53" s="15"/>
       <c r="BI53" s="15"/>
       <c r="BK53" s="19"/>
-      <c r="BO53" s="174"/>
-      <c r="BP53" s="174"/>
-      <c r="BQ53" s="174"/>
-      <c r="BR53" s="174"/>
-      <c r="BS53" s="174"/>
-      <c r="BT53" s="174"/>
-      <c r="BU53" s="174"/>
-      <c r="BV53" s="174"/>
-      <c r="BW53" s="174"/>
-      <c r="BX53" s="174"/>
-      <c r="BY53" s="174"/>
-      <c r="BZ53" s="174"/>
-      <c r="CA53" s="174"/>
-      <c r="CB53" s="174"/>
-      <c r="CC53" s="174"/>
-      <c r="CD53" s="174"/>
-      <c r="CE53" s="174"/>
-      <c r="CF53" s="174"/>
-      <c r="CG53" s="174"/>
-      <c r="CH53" s="174"/>
-      <c r="CI53" s="174"/>
+      <c r="BO53" s="149"/>
+      <c r="BP53" s="149"/>
+      <c r="BQ53" s="149"/>
+      <c r="BR53" s="149"/>
+      <c r="BS53" s="149"/>
+      <c r="BT53" s="149"/>
+      <c r="BU53" s="149"/>
+      <c r="BV53" s="149"/>
+      <c r="BW53" s="149"/>
+      <c r="BX53" s="149"/>
+      <c r="BY53" s="149"/>
+      <c r="BZ53" s="149"/>
+      <c r="CA53" s="149"/>
+      <c r="CB53" s="149"/>
+      <c r="CC53" s="149"/>
+      <c r="CD53" s="149"/>
+      <c r="CE53" s="149"/>
+      <c r="CF53" s="149"/>
+      <c r="CG53" s="149"/>
+      <c r="CH53" s="149"/>
+      <c r="CI53" s="149"/>
     </row>
     <row r="54" spans="2:87" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" s="137" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C54" s="95"/>
       <c r="D54" s="96"/>
@@ -4031,7 +4025,7 @@
         <v>1</v>
       </c>
       <c r="W54" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="X54" s="6"/>
       <c r="AO54" s="19"/>
@@ -4190,7 +4184,7 @@
       <c r="AO57" s="19"/>
       <c r="AQ57" s="11"/>
       <c r="AR57" s="20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AS57" s="15"/>
       <c r="AT57" s="15"/>
@@ -4379,7 +4373,7 @@
         <v>4</v>
       </c>
       <c r="AR61" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AT61" s="22"/>
       <c r="AU61" s="22"/>
@@ -4525,23 +4519,23 @@
       <c r="BI64" s="22"/>
       <c r="BK64" s="19"/>
       <c r="BO64" s="32"/>
-      <c r="BP64" s="174"/>
-      <c r="BQ64" s="174"/>
-      <c r="BR64" s="174"/>
-      <c r="BS64" s="174"/>
-      <c r="BT64" s="174"/>
-      <c r="BU64" s="174"/>
-      <c r="BV64" s="174"/>
-      <c r="BW64" s="174"/>
-      <c r="BX64" s="174"/>
-      <c r="BY64" s="174"/>
-      <c r="BZ64" s="174"/>
-      <c r="CA64" s="174"/>
-      <c r="CB64" s="174"/>
-      <c r="CC64" s="174"/>
-      <c r="CD64" s="174"/>
-      <c r="CE64" s="174"/>
-      <c r="CF64" s="174"/>
+      <c r="BP64" s="149"/>
+      <c r="BQ64" s="149"/>
+      <c r="BR64" s="149"/>
+      <c r="BS64" s="149"/>
+      <c r="BT64" s="149"/>
+      <c r="BU64" s="149"/>
+      <c r="BV64" s="149"/>
+      <c r="BW64" s="149"/>
+      <c r="BX64" s="149"/>
+      <c r="BY64" s="149"/>
+      <c r="BZ64" s="149"/>
+      <c r="CA64" s="149"/>
+      <c r="CB64" s="149"/>
+      <c r="CC64" s="149"/>
+      <c r="CD64" s="149"/>
+      <c r="CE64" s="149"/>
+      <c r="CF64" s="149"/>
     </row>
     <row r="65" spans="2:84" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B65" s="38"/>
@@ -4639,28 +4633,28 @@
       <c r="R67" s="26"/>
       <c r="S67" s="26"/>
       <c r="T67" s="112"/>
-      <c r="V67" s="156" t="s">
+      <c r="V67" s="150" t="s">
         <v>25</v>
       </c>
-      <c r="W67" s="157"/>
-      <c r="X67" s="157"/>
-      <c r="Y67" s="157"/>
-      <c r="Z67" s="157"/>
-      <c r="AA67" s="157"/>
-      <c r="AB67" s="157"/>
-      <c r="AC67" s="157"/>
-      <c r="AD67" s="157"/>
-      <c r="AE67" s="157"/>
-      <c r="AF67" s="157"/>
-      <c r="AG67" s="157"/>
-      <c r="AH67" s="157"/>
-      <c r="AI67" s="157"/>
-      <c r="AJ67" s="157"/>
-      <c r="AK67" s="157"/>
-      <c r="AL67" s="157"/>
-      <c r="AM67" s="157"/>
-      <c r="AN67" s="157"/>
-      <c r="AO67" s="158"/>
+      <c r="W67" s="151"/>
+      <c r="X67" s="151"/>
+      <c r="Y67" s="151"/>
+      <c r="Z67" s="151"/>
+      <c r="AA67" s="151"/>
+      <c r="AB67" s="151"/>
+      <c r="AC67" s="151"/>
+      <c r="AD67" s="151"/>
+      <c r="AE67" s="151"/>
+      <c r="AF67" s="151"/>
+      <c r="AG67" s="151"/>
+      <c r="AH67" s="151"/>
+      <c r="AI67" s="151"/>
+      <c r="AJ67" s="151"/>
+      <c r="AK67" s="151"/>
+      <c r="AL67" s="151"/>
+      <c r="AM67" s="151"/>
+      <c r="AN67" s="151"/>
+      <c r="AO67" s="152"/>
       <c r="AP67" s="70"/>
       <c r="AS67" s="22"/>
       <c r="AT67" s="22"/>
@@ -5013,24 +5007,24 @@
       <c r="AO76" s="19"/>
       <c r="AP76" s="19"/>
       <c r="BK76" s="19"/>
-      <c r="BO76" s="174"/>
-      <c r="BP76" s="174"/>
-      <c r="BQ76" s="174"/>
-      <c r="BR76" s="174"/>
-      <c r="BS76" s="174"/>
-      <c r="BT76" s="174"/>
-      <c r="BU76" s="174"/>
-      <c r="BV76" s="174"/>
-      <c r="BW76" s="174"/>
-      <c r="BX76" s="174"/>
-      <c r="BY76" s="174"/>
-      <c r="BZ76" s="174"/>
-      <c r="CA76" s="174"/>
-      <c r="CB76" s="174"/>
-      <c r="CC76" s="174"/>
-      <c r="CD76" s="174"/>
-      <c r="CE76" s="174"/>
-      <c r="CF76" s="174"/>
+      <c r="BO76" s="149"/>
+      <c r="BP76" s="149"/>
+      <c r="BQ76" s="149"/>
+      <c r="BR76" s="149"/>
+      <c r="BS76" s="149"/>
+      <c r="BT76" s="149"/>
+      <c r="BU76" s="149"/>
+      <c r="BV76" s="149"/>
+      <c r="BW76" s="149"/>
+      <c r="BX76" s="149"/>
+      <c r="BY76" s="149"/>
+      <c r="BZ76" s="149"/>
+      <c r="CA76" s="149"/>
+      <c r="CB76" s="149"/>
+      <c r="CC76" s="149"/>
+      <c r="CD76" s="149"/>
+      <c r="CE76" s="149"/>
+      <c r="CF76" s="149"/>
     </row>
     <row r="77" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B77" s="30"/>
@@ -5075,93 +5069,93 @@
       <c r="BK81" s="53"/>
     </row>
     <row r="82" spans="2:63" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="156" t="s">
+      <c r="B82" s="150" t="s">
         <v>26</v>
       </c>
-      <c r="C82" s="157"/>
-      <c r="D82" s="157"/>
-      <c r="E82" s="157"/>
-      <c r="F82" s="157"/>
-      <c r="G82" s="157"/>
-      <c r="H82" s="157"/>
-      <c r="I82" s="157"/>
-      <c r="J82" s="157"/>
-      <c r="K82" s="157"/>
-      <c r="L82" s="157"/>
-      <c r="M82" s="157"/>
-      <c r="N82" s="157"/>
-      <c r="O82" s="157"/>
-      <c r="P82" s="157"/>
-      <c r="Q82" s="157"/>
-      <c r="R82" s="157"/>
-      <c r="S82" s="157"/>
-      <c r="T82" s="157"/>
-      <c r="U82" s="157"/>
-      <c r="V82" s="157"/>
-      <c r="W82" s="157"/>
-      <c r="X82" s="157"/>
-      <c r="Y82" s="157"/>
-      <c r="Z82" s="157"/>
-      <c r="AA82" s="157"/>
-      <c r="AB82" s="157"/>
-      <c r="AC82" s="157"/>
-      <c r="AD82" s="157"/>
-      <c r="AE82" s="157"/>
-      <c r="AF82" s="157"/>
-      <c r="AG82" s="157"/>
-      <c r="AH82" s="157"/>
-      <c r="AI82" s="157"/>
-      <c r="AJ82" s="157"/>
-      <c r="AK82" s="157"/>
-      <c r="AL82" s="157"/>
-      <c r="AM82" s="157"/>
-      <c r="AN82" s="157"/>
-      <c r="AO82" s="157"/>
-      <c r="AP82" s="157"/>
-      <c r="AQ82" s="157"/>
-      <c r="AR82" s="157"/>
-      <c r="AS82" s="157"/>
-      <c r="AT82" s="157"/>
-      <c r="AU82" s="157"/>
-      <c r="AV82" s="157"/>
-      <c r="AW82" s="157"/>
-      <c r="AX82" s="157"/>
-      <c r="AY82" s="157"/>
-      <c r="AZ82" s="157"/>
-      <c r="BA82" s="157"/>
-      <c r="BB82" s="157"/>
-      <c r="BC82" s="157"/>
-      <c r="BD82" s="157"/>
-      <c r="BE82" s="157"/>
-      <c r="BF82" s="157"/>
-      <c r="BG82" s="157"/>
-      <c r="BH82" s="157"/>
-      <c r="BI82" s="157"/>
-      <c r="BJ82" s="157"/>
-      <c r="BK82" s="158"/>
+      <c r="C82" s="151"/>
+      <c r="D82" s="151"/>
+      <c r="E82" s="151"/>
+      <c r="F82" s="151"/>
+      <c r="G82" s="151"/>
+      <c r="H82" s="151"/>
+      <c r="I82" s="151"/>
+      <c r="J82" s="151"/>
+      <c r="K82" s="151"/>
+      <c r="L82" s="151"/>
+      <c r="M82" s="151"/>
+      <c r="N82" s="151"/>
+      <c r="O82" s="151"/>
+      <c r="P82" s="151"/>
+      <c r="Q82" s="151"/>
+      <c r="R82" s="151"/>
+      <c r="S82" s="151"/>
+      <c r="T82" s="151"/>
+      <c r="U82" s="151"/>
+      <c r="V82" s="151"/>
+      <c r="W82" s="151"/>
+      <c r="X82" s="151"/>
+      <c r="Y82" s="151"/>
+      <c r="Z82" s="151"/>
+      <c r="AA82" s="151"/>
+      <c r="AB82" s="151"/>
+      <c r="AC82" s="151"/>
+      <c r="AD82" s="151"/>
+      <c r="AE82" s="151"/>
+      <c r="AF82" s="151"/>
+      <c r="AG82" s="151"/>
+      <c r="AH82" s="151"/>
+      <c r="AI82" s="151"/>
+      <c r="AJ82" s="151"/>
+      <c r="AK82" s="151"/>
+      <c r="AL82" s="151"/>
+      <c r="AM82" s="151"/>
+      <c r="AN82" s="151"/>
+      <c r="AO82" s="151"/>
+      <c r="AP82" s="151"/>
+      <c r="AQ82" s="151"/>
+      <c r="AR82" s="151"/>
+      <c r="AS82" s="151"/>
+      <c r="AT82" s="151"/>
+      <c r="AU82" s="151"/>
+      <c r="AV82" s="151"/>
+      <c r="AW82" s="151"/>
+      <c r="AX82" s="151"/>
+      <c r="AY82" s="151"/>
+      <c r="AZ82" s="151"/>
+      <c r="BA82" s="151"/>
+      <c r="BB82" s="151"/>
+      <c r="BC82" s="151"/>
+      <c r="BD82" s="151"/>
+      <c r="BE82" s="151"/>
+      <c r="BF82" s="151"/>
+      <c r="BG82" s="151"/>
+      <c r="BH82" s="151"/>
+      <c r="BI82" s="151"/>
+      <c r="BJ82" s="151"/>
+      <c r="BK82" s="152"/>
     </row>
     <row r="83" spans="2:63" ht="13.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="168" t="s">
+      <c r="B83" s="153" t="s">
         <v>27</v>
       </c>
-      <c r="C83" s="169"/>
-      <c r="D83" s="169"/>
-      <c r="E83" s="169"/>
-      <c r="F83" s="169"/>
-      <c r="G83" s="169"/>
-      <c r="H83" s="169"/>
-      <c r="I83" s="169"/>
-      <c r="J83" s="169"/>
-      <c r="K83" s="169"/>
-      <c r="L83" s="169"/>
-      <c r="M83" s="169"/>
-      <c r="N83" s="169"/>
-      <c r="O83" s="169"/>
-      <c r="P83" s="169"/>
-      <c r="Q83" s="169"/>
-      <c r="R83" s="169"/>
-      <c r="S83" s="169"/>
-      <c r="T83" s="169"/>
+      <c r="C83" s="154"/>
+      <c r="D83" s="154"/>
+      <c r="E83" s="154"/>
+      <c r="F83" s="154"/>
+      <c r="G83" s="154"/>
+      <c r="H83" s="154"/>
+      <c r="I83" s="154"/>
+      <c r="J83" s="154"/>
+      <c r="K83" s="154"/>
+      <c r="L83" s="154"/>
+      <c r="M83" s="154"/>
+      <c r="N83" s="154"/>
+      <c r="O83" s="154"/>
+      <c r="P83" s="154"/>
+      <c r="Q83" s="154"/>
+      <c r="R83" s="154"/>
+      <c r="S83" s="154"/>
+      <c r="T83" s="154"/>
       <c r="U83" s="45"/>
       <c r="V83" s="118" t="s">
         <v>28</v>
@@ -5193,7 +5187,7 @@
       <c r="S84" s="26"/>
       <c r="T84" s="26"/>
       <c r="V84" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="W84" s="26"/>
       <c r="AQ84" s="120" t="s">
@@ -5229,11 +5223,8 @@
       <c r="BK85" s="19"/>
     </row>
     <row r="86" spans="2:63" x14ac:dyDescent="0.25">
-      <c r="B86" s="146" t="s">
-        <v>64</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>59</v>
+      <c r="B86" s="177" t="s">
+        <v>58</v>
       </c>
       <c r="E86" s="26"/>
       <c r="F86" s="26"/>
@@ -5251,27 +5242,18 @@
       <c r="R86" s="26"/>
       <c r="S86" s="26"/>
       <c r="T86" s="26"/>
-      <c r="V86" s="37" t="s">
+      <c r="V86" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="AQ86" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="W86" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ86" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="AR86" s="135" t="s">
-        <v>50</v>
-      </c>
+      <c r="AR86" s="135"/>
       <c r="BK86" s="19"/>
     </row>
     <row r="87" spans="2:63" x14ac:dyDescent="0.25">
-      <c r="B87" s="94" t="s">
-        <v>65</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>50</v>
-      </c>
+      <c r="B87" s="94"/>
+      <c r="C87" s="7"/>
       <c r="D87" s="26"/>
       <c r="E87" s="26"/>
       <c r="F87" s="26"/>
@@ -5289,27 +5271,15 @@
       <c r="R87" s="26"/>
       <c r="S87" s="26"/>
       <c r="T87" s="26"/>
-      <c r="V87" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="W87" s="145" t="s">
-        <v>50</v>
-      </c>
-      <c r="AQ87" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="AR87" s="135" t="s">
-        <v>50</v>
-      </c>
+      <c r="V87" s="37"/>
+      <c r="W87" s="145"/>
+      <c r="AQ87" s="37"/>
+      <c r="AR87" s="135"/>
       <c r="BK87" s="19"/>
     </row>
     <row r="88" spans="2:63" x14ac:dyDescent="0.25">
-      <c r="B88" s="146" t="s">
-        <v>66</v>
-      </c>
-      <c r="C88" s="44" t="s">
-        <v>50</v>
-      </c>
+      <c r="B88" s="146"/>
+      <c r="C88" s="44"/>
       <c r="D88" s="26"/>
       <c r="E88" s="26"/>
       <c r="F88" s="26"/>
@@ -5327,18 +5297,10 @@
       <c r="R88" s="26"/>
       <c r="S88" s="26"/>
       <c r="T88" s="26"/>
-      <c r="V88" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="W88" s="145" t="s">
-        <v>50</v>
-      </c>
-      <c r="AQ88" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR88" s="135" t="s">
-        <v>50</v>
-      </c>
+      <c r="V88" s="27"/>
+      <c r="W88" s="145"/>
+      <c r="AQ88" s="27"/>
+      <c r="AR88" s="135"/>
       <c r="BK88" s="19"/>
     </row>
     <row r="89" spans="2:63" x14ac:dyDescent="0.25">
@@ -5528,11 +5490,12 @@
     <row r="96" spans="2:63" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="BO53:CI53"/>
-    <mergeCell ref="BP64:CF64"/>
-    <mergeCell ref="V67:AO67"/>
-    <mergeCell ref="BO76:CF76"/>
-    <mergeCell ref="B82:BK82"/>
+    <mergeCell ref="M2:AO5"/>
+    <mergeCell ref="X12:AO12"/>
+    <mergeCell ref="B8:W8"/>
+    <mergeCell ref="X8:AO8"/>
+    <mergeCell ref="AQ8:BK8"/>
+    <mergeCell ref="X9:AO11"/>
     <mergeCell ref="B83:T83"/>
     <mergeCell ref="B23:BK23"/>
     <mergeCell ref="B45:BK45"/>
@@ -5540,12 +5503,11 @@
     <mergeCell ref="V52:AO52"/>
     <mergeCell ref="AQ52:BK52"/>
     <mergeCell ref="M46:AO49"/>
-    <mergeCell ref="M2:AO5"/>
-    <mergeCell ref="X12:AO12"/>
-    <mergeCell ref="B8:W8"/>
-    <mergeCell ref="X8:AO8"/>
-    <mergeCell ref="AQ8:BK8"/>
-    <mergeCell ref="X9:AO11"/>
+    <mergeCell ref="BO53:CI53"/>
+    <mergeCell ref="BP64:CF64"/>
+    <mergeCell ref="V67:AO67"/>
+    <mergeCell ref="BO76:CF76"/>
+    <mergeCell ref="B82:BK82"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0.19685039370078741" header="3.937007874015748E-2" footer="0.23622047244094491"/>
